--- a/Data/Salmon/Market/Exports.xlsx
+++ b/Data/Salmon/Market/Exports.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6318875413f076c7/Escritorio/Work/Master Thesis/Laks/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fillipaskildsen/Documents/GitHub/Data/Salmon/Market/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{59A528A3-71CD-CB46-841E-11D70D0ED9F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F7E8701-3CB7-4AA8-A260-EE5011C8145C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E58DB1D-616B-F64A-AD47-C4B6A774FA10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -167,7 +167,14 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -178,6 +185,34 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AF9EF88E-A16D-5343-A5E8-4BC069E93249}" name="Table1" displayName="Table1" ref="A1:N265" totalsRowShown="0">
+  <autoFilter ref="A1:N265" xr:uid="{AF9EF88E-A16D-5343-A5E8-4BC069E93249}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N265">
+    <sortCondition ref="B1:B265"/>
+  </sortState>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{F35194DE-B5A7-5249-9609-75201F8CE621}" name="freqCode"/>
+    <tableColumn id="2" xr3:uid="{39C24010-2EB5-1B41-AB8D-BC902CC4CC4B}" name="refPeriodId"/>
+    <tableColumn id="3" xr3:uid="{697FDA84-1621-4A42-A47D-72DDD359D073}" name="ReleaseDate"/>
+    <tableColumn id="4" xr3:uid="{738CB3A8-EEAE-B64A-86C0-4A00114107A5}" name="reporterISO"/>
+    <tableColumn id="5" xr3:uid="{13E2C87F-9598-5742-BE63-8B1EC6672929}" name="flowDesc"/>
+    <tableColumn id="6" xr3:uid="{C35EFBB0-050A-9A49-9B4D-0FBEB15225E0}" name="partnerISO"/>
+    <tableColumn id="7" xr3:uid="{FAB5D6B5-5E03-904B-9C1C-4D64485B045D}" name="cmdCode" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{8726BDD2-14BE-B44F-B1C1-E64B4AE2269E}" name="cmdDesc"/>
+    <tableColumn id="9" xr3:uid="{727CCCAB-D16C-1641-8930-D9239D0961BA}" name="customsCode"/>
+    <tableColumn id="10" xr3:uid="{C4FC6F10-408E-B14C-B2EE-D3487D77318A}" name="motDesc"/>
+    <tableColumn id="11" xr3:uid="{66F33009-886F-854E-9DAF-8FA79ED9D892}" name="QtyUnit"/>
+    <tableColumn id="12" xr3:uid="{6DF84CB4-0776-854A-B8BF-434ED4D3379D}" name="netWgt"/>
+    <tableColumn id="13" xr3:uid="{4FE1CE5F-913C-B548-8E7B-6B5895FC09C1}" name="primaryValueUSD"/>
+    <tableColumn id="14" xr3:uid="{D5197674-0FE2-5849-8E6B-D92F904242CD}" name="AvgValueKg" dataDxfId="0">
+      <calculatedColumnFormula>M2/L2</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -503,18 +538,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N265"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.6875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5" customWidth="1"/>
+    <col min="3" max="3" width="13.83203125" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="8" width="209.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" customWidth="1"/>
     <col min="11" max="11" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.6875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.8125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="14" max="14" width="13.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -558,7 +596,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -603,7 +641,7 @@
         <v>3.6929803182262475</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -644,11 +682,11 @@
         <v>96031734.523000002</v>
       </c>
       <c r="N3" s="4">
-        <f t="shared" ref="N3:N66" si="0">M3/L3</f>
+        <f>M3/L3</f>
         <v>3.8895793567797732</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -689,11 +727,11 @@
         <v>122072922.15000001</v>
       </c>
       <c r="N4" s="4">
-        <f t="shared" si="0"/>
+        <f>M4/L4</f>
         <v>3.9761199486579151</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -734,11 +772,11 @@
         <v>122306911.91500001</v>
       </c>
       <c r="N5" s="4">
-        <f t="shared" si="0"/>
+        <f>M5/L5</f>
         <v>3.9764836929165437</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -779,11 +817,11 @@
         <v>102490948.37</v>
       </c>
       <c r="N6" s="4">
-        <f t="shared" si="0"/>
+        <f>M6/L6</f>
         <v>3.994178832256174</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -824,11 +862,11 @@
         <v>126527719.164</v>
       </c>
       <c r="N7" s="4">
-        <f t="shared" si="0"/>
+        <f>M7/L7</f>
         <v>4.1954483211952285</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -869,11 +907,11 @@
         <v>123501801.382</v>
       </c>
       <c r="N8" s="4">
-        <f t="shared" si="0"/>
+        <f>M8/L8</f>
         <v>4.3795701169587034</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -914,11 +952,11 @@
         <v>126356547.507</v>
       </c>
       <c r="N9" s="4">
-        <f t="shared" si="0"/>
+        <f>M9/L9</f>
         <v>4.3358894770584309</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -959,11 +997,11 @@
         <v>155530520.62799999</v>
       </c>
       <c r="N10" s="4">
-        <f t="shared" si="0"/>
+        <f>M10/L10</f>
         <v>4.1809444953451829</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1004,11 +1042,11 @@
         <v>141067503.829</v>
       </c>
       <c r="N11" s="4">
-        <f t="shared" si="0"/>
+        <f>M11/L11</f>
         <v>4.0216876724667285</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1049,11 +1087,11 @@
         <v>158660088.62400001</v>
       </c>
       <c r="N12" s="4">
-        <f t="shared" si="0"/>
+        <f>M12/L12</f>
         <v>3.9270596142464318</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -1094,11 +1132,11 @@
         <v>187034414.39300001</v>
       </c>
       <c r="N13" s="4">
-        <f t="shared" si="0"/>
+        <f>M13/L13</f>
         <v>4.131951173675751</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -1139,11 +1177,11 @@
         <v>108006902.90700001</v>
       </c>
       <c r="N14" s="4">
-        <f t="shared" si="0"/>
+        <f>M14/L14</f>
         <v>4.0271127766342465</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -1184,11 +1222,11 @@
         <v>110114065.59</v>
       </c>
       <c r="N15" s="4">
-        <f t="shared" si="0"/>
+        <f>M15/L15</f>
         <v>4.0054598826408299</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>10</v>
       </c>
@@ -1229,11 +1267,11 @@
         <v>167134819.94</v>
       </c>
       <c r="N16" s="4">
-        <f t="shared" si="0"/>
+        <f>M16/L16</f>
         <v>4.6158108972305376</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>10</v>
       </c>
@@ -1274,11 +1312,11 @@
         <v>159883604.713</v>
       </c>
       <c r="N17" s="4">
-        <f t="shared" si="0"/>
+        <f>M17/L17</f>
         <v>5.4307179151092084</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>10</v>
       </c>
@@ -1319,11 +1357,11 @@
         <v>178928024.87599999</v>
       </c>
       <c r="N18" s="4">
-        <f t="shared" si="0"/>
+        <f>M18/L18</f>
         <v>6.1768248027678334</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>10</v>
       </c>
@@ -1364,11 +1402,11 @@
         <v>213349075.52000001</v>
       </c>
       <c r="N19" s="4">
-        <f t="shared" si="0"/>
+        <f>M19/L19</f>
         <v>6.6855920408050071</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1409,11 +1447,11 @@
         <v>152482259.005</v>
       </c>
       <c r="N20" s="4">
-        <f t="shared" si="0"/>
+        <f>M20/L20</f>
         <v>6.1443017947437903</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>10</v>
       </c>
@@ -1454,11 +1492,11 @@
         <v>170818653.729</v>
       </c>
       <c r="N21" s="4">
-        <f t="shared" si="0"/>
+        <f>M21/L21</f>
         <v>5.8282790837922205</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>10</v>
       </c>
@@ -1499,11 +1537,11 @@
         <v>159856015.89700001</v>
       </c>
       <c r="N22" s="4">
-        <f t="shared" si="0"/>
+        <f>M22/L22</f>
         <v>4.7221605919939753</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>10</v>
       </c>
@@ -1544,11 +1582,11 @@
         <v>165548715.15000001</v>
       </c>
       <c r="N23" s="4">
-        <f t="shared" si="0"/>
+        <f>M23/L23</f>
         <v>4.2936249989107003</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>10</v>
       </c>
@@ -1589,11 +1627,11 @@
         <v>194807742.18799999</v>
       </c>
       <c r="N24" s="4">
-        <f t="shared" si="0"/>
+        <f>M24/L24</f>
         <v>4.3122813715520278</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>10</v>
       </c>
@@ -1634,11 +1672,11 @@
         <v>205491266.882</v>
       </c>
       <c r="N25" s="4">
-        <f t="shared" si="0"/>
+        <f>M25/L25</f>
         <v>4.5065941815137656</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>10</v>
       </c>
@@ -1679,11 +1717,11 @@
         <v>152176420.70300001</v>
       </c>
       <c r="N26" s="4">
-        <f t="shared" si="0"/>
+        <f>M26/L26</f>
         <v>4.4638385433159016</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>10</v>
       </c>
@@ -1724,11 +1762,11 @@
         <v>150158968.87599999</v>
       </c>
       <c r="N27" s="4">
-        <f t="shared" si="0"/>
+        <f>M27/L27</f>
         <v>4.623296756388366</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>10</v>
       </c>
@@ -1769,11 +1807,11 @@
         <v>209784933.85800001</v>
       </c>
       <c r="N28" s="4">
-        <f t="shared" si="0"/>
+        <f>M28/L28</f>
         <v>4.6993455894706315</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>10</v>
       </c>
@@ -1814,11 +1852,11 @@
         <v>165098935.53099999</v>
       </c>
       <c r="N29" s="4">
-        <f t="shared" si="0"/>
+        <f>M29/L29</f>
         <v>4.7762676098086478</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>10</v>
       </c>
@@ -1859,11 +1897,11 @@
         <v>179104505.537</v>
       </c>
       <c r="N30" s="4">
-        <f t="shared" si="0"/>
+        <f>M30/L30</f>
         <v>4.4315407893397474</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>10</v>
       </c>
@@ -1904,11 +1942,11 @@
         <v>186510538.57499999</v>
       </c>
       <c r="N31" s="4">
-        <f t="shared" si="0"/>
+        <f>M31/L31</f>
         <v>4.2227650682498385</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>10</v>
       </c>
@@ -1949,11 +1987,11 @@
         <v>164483645.051</v>
       </c>
       <c r="N32" s="4">
-        <f t="shared" si="0"/>
+        <f>M32/L32</f>
         <v>4.3517348547082433</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>10</v>
       </c>
@@ -1994,11 +2032,11 @@
         <v>180541522.706</v>
       </c>
       <c r="N33" s="4">
-        <f t="shared" si="0"/>
+        <f>M33/L33</f>
         <v>4.7337427880382421</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>10</v>
       </c>
@@ -2039,11 +2077,11 @@
         <v>192469967.21700001</v>
       </c>
       <c r="N34" s="4">
-        <f t="shared" si="0"/>
+        <f>M34/L34</f>
         <v>4.5779500659898522</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>10</v>
       </c>
@@ -2084,11 +2122,11 @@
         <v>201673416.70300001</v>
       </c>
       <c r="N35" s="4">
-        <f t="shared" si="0"/>
+        <f>M35/L35</f>
         <v>4.4771418044873492</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>10</v>
       </c>
@@ -2129,11 +2167,11 @@
         <v>236331776.56299999</v>
       </c>
       <c r="N36" s="4">
-        <f t="shared" si="0"/>
+        <f>M36/L36</f>
         <v>4.5035471872936172</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>10</v>
       </c>
@@ -2174,11 +2212,11 @@
         <v>224612788.47799999</v>
       </c>
       <c r="N37" s="4">
-        <f t="shared" si="0"/>
+        <f>M37/L37</f>
         <v>4.6711900000049908</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>10</v>
       </c>
@@ -2219,11 +2257,11 @@
         <v>183747776.759</v>
       </c>
       <c r="N38" s="4">
-        <f t="shared" si="0"/>
+        <f>M38/L38</f>
         <v>4.8120669809855192</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>10</v>
       </c>
@@ -2264,11 +2302,11 @@
         <v>192783643.82600001</v>
       </c>
       <c r="N39" s="4">
-        <f t="shared" si="0"/>
+        <f>M39/L39</f>
         <v>4.7361892887740655</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>10</v>
       </c>
@@ -2309,11 +2347,11 @@
         <v>212520269.91499999</v>
       </c>
       <c r="N40" s="4">
-        <f t="shared" si="0"/>
+        <f>M40/L40</f>
         <v>5.2238633481903038</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>10</v>
       </c>
@@ -2354,11 +2392,11 @@
         <v>205398205.491</v>
       </c>
       <c r="N41" s="4">
-        <f t="shared" si="0"/>
+        <f>M41/L41</f>
         <v>5.1208796314759439</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>10</v>
       </c>
@@ -2399,11 +2437,11 @@
         <v>236900787</v>
       </c>
       <c r="N42" s="4">
-        <f t="shared" si="0"/>
+        <f>M42/L42</f>
         <v>5.3123928204763207</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>10</v>
       </c>
@@ -2444,11 +2482,11 @@
         <v>211447611.31299999</v>
       </c>
       <c r="N43" s="4">
-        <f t="shared" si="0"/>
+        <f>M43/L43</f>
         <v>5.1508816441429675</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>10</v>
       </c>
@@ -2489,11 +2527,11 @@
         <v>222405826</v>
       </c>
       <c r="N44" s="4">
-        <f t="shared" si="0"/>
+        <f>M44/L44</f>
         <v>5.6246986287526051</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>10</v>
       </c>
@@ -2534,11 +2572,11 @@
         <v>202942113.22</v>
       </c>
       <c r="N45" s="4">
-        <f t="shared" si="0"/>
+        <f>M45/L45</f>
         <v>5.3665764935713876</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>10</v>
       </c>
@@ -2579,11 +2617,11 @@
         <v>207063689.93700001</v>
       </c>
       <c r="N46" s="4">
-        <f t="shared" si="0"/>
+        <f>M46/L46</f>
         <v>4.9568312585001761</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>10</v>
       </c>
@@ -2624,11 +2662,11 @@
         <v>200125937.141</v>
       </c>
       <c r="N47" s="4">
-        <f t="shared" si="0"/>
+        <f>M47/L47</f>
         <v>4.1565689181446279</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>10</v>
       </c>
@@ -2669,11 +2707,11 @@
         <v>186704409.067</v>
       </c>
       <c r="N48" s="4">
-        <f t="shared" si="0"/>
+        <f>M48/L48</f>
         <v>3.8183936547976738</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>10</v>
       </c>
@@ -2714,11 +2752,11 @@
         <v>200629029.69499999</v>
       </c>
       <c r="N49" s="4">
-        <f t="shared" si="0"/>
+        <f>M49/L49</f>
         <v>3.9017650811592648</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>10</v>
       </c>
@@ -2759,11 +2797,11 @@
         <v>173072988.917</v>
       </c>
       <c r="N50" s="4">
-        <f t="shared" si="0"/>
+        <f>M50/L50</f>
         <v>4.1152659968602583</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>10</v>
       </c>
@@ -2804,11 +2842,11 @@
         <v>150547493.45899999</v>
       </c>
       <c r="N51" s="4">
-        <f t="shared" si="0"/>
+        <f>M51/L51</f>
         <v>4.1208041572941099</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>10</v>
       </c>
@@ -2849,11 +2887,11 @@
         <v>200693084.685</v>
       </c>
       <c r="N52" s="4">
-        <f t="shared" si="0"/>
+        <f>M52/L52</f>
         <v>4.476224733160306</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>10</v>
       </c>
@@ -2894,11 +2932,11 @@
         <v>213599730.708</v>
       </c>
       <c r="N53" s="4">
-        <f t="shared" si="0"/>
+        <f>M53/L53</f>
         <v>4.7946969397089898</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>10</v>
       </c>
@@ -2939,11 +2977,11 @@
         <v>239825384.52000001</v>
       </c>
       <c r="N54" s="4">
-        <f t="shared" si="0"/>
+        <f>M54/L54</f>
         <v>5.4411179084106314</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>10</v>
       </c>
@@ -2984,11 +3022,11 @@
         <v>242800231.30500001</v>
       </c>
       <c r="N55" s="4">
-        <f t="shared" si="0"/>
+        <f>M55/L55</f>
         <v>5.522968585166244</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>10</v>
       </c>
@@ -3029,11 +3067,11 @@
         <v>261254096.546</v>
       </c>
       <c r="N56" s="4">
-        <f t="shared" si="0"/>
+        <f>M56/L56</f>
         <v>5.7833570178879912</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>10</v>
       </c>
@@ -3074,11 +3112,11 @@
         <v>226420292.23899999</v>
       </c>
       <c r="N57" s="4">
-        <f t="shared" si="0"/>
+        <f>M57/L57</f>
         <v>4.9928416749500206</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>10</v>
       </c>
@@ -3119,11 +3157,11 @@
         <v>253470021.06999999</v>
       </c>
       <c r="N58" s="4">
-        <f t="shared" si="0"/>
+        <f>M58/L58</f>
         <v>5.0039297056810277</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>10</v>
       </c>
@@ -3164,11 +3202,11 @@
         <v>269610019.52499998</v>
       </c>
       <c r="N59" s="4">
-        <f t="shared" si="0"/>
+        <f>M59/L59</f>
         <v>4.8321213784676837</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>10</v>
       </c>
@@ -3209,11 +3247,11 @@
         <v>274847740.43099999</v>
       </c>
       <c r="N60" s="4">
-        <f t="shared" si="0"/>
+        <f>M60/L60</f>
         <v>5.0096604295562592</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>10</v>
       </c>
@@ -3254,11 +3292,11 @@
         <v>315373763.417</v>
       </c>
       <c r="N61" s="4">
-        <f t="shared" si="0"/>
+        <f>M61/L61</f>
         <v>5.0394455454753997</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>10</v>
       </c>
@@ -3299,11 +3337,11 @@
         <v>224249132.639</v>
       </c>
       <c r="N62" s="4">
-        <f t="shared" si="0"/>
+        <f>M62/L62</f>
         <v>5.0922179286730218</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>10</v>
       </c>
@@ -3344,11 +3382,11 @@
         <v>236280374.73199999</v>
       </c>
       <c r="N63" s="4">
-        <f t="shared" si="0"/>
+        <f>M63/L63</f>
         <v>5.6881391588953205</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>10</v>
       </c>
@@ -3389,11 +3427,11 @@
         <v>328364302.88499999</v>
       </c>
       <c r="N64" s="4">
-        <f t="shared" si="0"/>
+        <f>M64/L64</f>
         <v>6.0899560345098429</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>10</v>
       </c>
@@ -3434,11 +3472,11 @@
         <v>282823422.07300001</v>
       </c>
       <c r="N65" s="4">
-        <f t="shared" si="0"/>
+        <f>M65/L65</f>
         <v>6.559412959658661</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>10</v>
       </c>
@@ -3479,11 +3517,11 @@
         <v>292687557.35600001</v>
       </c>
       <c r="N66" s="4">
-        <f t="shared" si="0"/>
+        <f>M66/L66</f>
         <v>6.3569436686558429</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>10</v>
       </c>
@@ -3524,11 +3562,11 @@
         <v>310461937.64600003</v>
       </c>
       <c r="N67" s="4">
-        <f t="shared" ref="N67:N130" si="1">M67/L67</f>
+        <f>M67/L67</f>
         <v>5.9463340789220291</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>10</v>
       </c>
@@ -3569,11 +3607,11 @@
         <v>315610175.417</v>
       </c>
       <c r="N68" s="4">
-        <f t="shared" si="1"/>
+        <f>M68/L68</f>
         <v>6.279581084605474</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>10</v>
       </c>
@@ -3614,11 +3652,11 @@
         <v>298004320.85600001</v>
       </c>
       <c r="N69" s="4">
-        <f t="shared" si="1"/>
+        <f>M69/L69</f>
         <v>6.4668394688753255</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>10</v>
       </c>
@@ -3659,11 +3697,11 @@
         <v>348444218.13999999</v>
       </c>
       <c r="N70" s="4">
-        <f t="shared" si="1"/>
+        <f>M70/L70</f>
         <v>6.1553043076080147</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>10</v>
       </c>
@@ -3704,11 +3742,11 @@
         <v>373227363.07300001</v>
       </c>
       <c r="N71" s="4">
-        <f t="shared" si="1"/>
+        <f>M71/L71</f>
         <v>6.3029942866498709</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>10</v>
       </c>
@@ -3749,11 +3787,11 @@
         <v>368593591.36199999</v>
       </c>
       <c r="N72" s="4">
-        <f t="shared" si="1"/>
+        <f>M72/L72</f>
         <v>6.0502456418146018</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>10</v>
       </c>
@@ -3794,11 +3832,11 @@
         <v>451344785.02700001</v>
       </c>
       <c r="N73" s="4">
-        <f t="shared" si="1"/>
+        <f>M73/L73</f>
         <v>7.0437525325185266</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>10</v>
       </c>
@@ -3839,11 +3877,11 @@
         <v>299397808.97799999</v>
       </c>
       <c r="N74" s="4">
-        <f t="shared" si="1"/>
+        <f>M74/L74</f>
         <v>6.7481162211273338</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>10</v>
       </c>
@@ -3884,11 +3922,11 @@
         <v>302531127.53899997</v>
       </c>
       <c r="N75" s="4">
-        <f t="shared" si="1"/>
+        <f>M75/L75</f>
         <v>7.0835316624818025</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>10</v>
       </c>
@@ -3929,11 +3967,11 @@
         <v>386945832.72299999</v>
       </c>
       <c r="N76" s="4">
-        <f t="shared" si="1"/>
+        <f>M76/L76</f>
         <v>7.2798797594925331</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>10</v>
       </c>
@@ -3974,11 +4012,11 @@
         <v>374303629.78399998</v>
       </c>
       <c r="N77" s="4">
-        <f t="shared" si="1"/>
+        <f>M77/L77</f>
         <v>7.9021572064357004</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>10</v>
       </c>
@@ -4019,11 +4057,11 @@
         <v>363957757.31</v>
       </c>
       <c r="N78" s="4">
-        <f t="shared" si="1"/>
+        <f>M78/L78</f>
         <v>7.1951184649670932</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>10</v>
       </c>
@@ -4064,11 +4102,11 @@
         <v>324534066.09899998</v>
       </c>
       <c r="N79" s="4">
-        <f t="shared" si="1"/>
+        <f>M79/L79</f>
         <v>6.0134687950406924</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>10</v>
       </c>
@@ -4109,11 +4147,11 @@
         <v>300336825.85299999</v>
       </c>
       <c r="N80" s="4">
-        <f t="shared" si="1"/>
+        <f>M80/L80</f>
         <v>5.6955780871458446</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>10</v>
       </c>
@@ -4154,11 +4192,11 @@
         <v>289416235.66799998</v>
       </c>
       <c r="N81" s="4">
-        <f t="shared" si="1"/>
+        <f>M81/L81</f>
         <v>5.2234959750655046</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>10</v>
       </c>
@@ -4199,11 +4237,11 @@
         <v>311214557.44</v>
       </c>
       <c r="N82" s="4">
-        <f t="shared" si="1"/>
+        <f>M82/L82</f>
         <v>4.711811166830449</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>10</v>
       </c>
@@ -4244,11 +4282,11 @@
         <v>278901328.08600003</v>
       </c>
       <c r="N83" s="4">
-        <f t="shared" si="1"/>
+        <f>M83/L83</f>
         <v>4.1299812194996086</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>10</v>
       </c>
@@ -4289,11 +4327,11 @@
         <v>318586117.39700001</v>
       </c>
       <c r="N84" s="4">
-        <f t="shared" si="1"/>
+        <f>M84/L84</f>
         <v>4.3595106773392942</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>10</v>
       </c>
@@ -4334,11 +4372,11 @@
         <v>358897044.44700003</v>
       </c>
       <c r="N85" s="4">
-        <f t="shared" si="1"/>
+        <f>M85/L85</f>
         <v>4.5755047164548239</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>10</v>
       </c>
@@ -4379,11 +4417,11 @@
         <v>241835255.539</v>
       </c>
       <c r="N86" s="4">
-        <f t="shared" si="1"/>
+        <f>M86/L86</f>
         <v>4.3241045672641301</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>10</v>
       </c>
@@ -4424,11 +4462,11 @@
         <v>280092193.22799999</v>
       </c>
       <c r="N87" s="4">
-        <f t="shared" si="1"/>
+        <f>M87/L87</f>
         <v>4.9283740583569537</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>10</v>
       </c>
@@ -4469,11 +4507,11 @@
         <v>367270313.78899997</v>
       </c>
       <c r="N88" s="4">
-        <f t="shared" si="1"/>
+        <f>M88/L88</f>
         <v>4.9288204135014695</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>10</v>
       </c>
@@ -4514,11 +4552,11 @@
         <v>296636579.57999998</v>
       </c>
       <c r="N89" s="4">
-        <f t="shared" si="1"/>
+        <f>M89/L89</f>
         <v>5.0688533089165251</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>10</v>
       </c>
@@ -4559,11 +4597,11 @@
         <v>331319655.50700003</v>
       </c>
       <c r="N90" s="4">
-        <f t="shared" si="1"/>
+        <f>M90/L90</f>
         <v>5.0079421054415967</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>10</v>
       </c>
@@ -4604,11 +4642,11 @@
         <v>321676419.51599997</v>
       </c>
       <c r="N91" s="4">
-        <f t="shared" si="1"/>
+        <f>M91/L91</f>
         <v>4.4495736646821609</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>10</v>
       </c>
@@ -4649,11 +4687,11 @@
         <v>287006621.51099998</v>
       </c>
       <c r="N92" s="4">
-        <f t="shared" si="1"/>
+        <f>M92/L92</f>
         <v>4.4390043983796055</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>10</v>
       </c>
@@ -4694,11 +4732,11 @@
         <v>339851093.94300002</v>
       </c>
       <c r="N93" s="4">
-        <f t="shared" si="1"/>
+        <f>M93/L93</f>
         <v>4.7328086268079543</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>10</v>
       </c>
@@ -4739,11 +4777,11 @@
         <v>323484317.56400001</v>
       </c>
       <c r="N94" s="4">
-        <f t="shared" si="1"/>
+        <f>M94/L94</f>
         <v>4.5786591128763972</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>10</v>
       </c>
@@ -4784,11 +4822,11 @@
         <v>348732469.76899999</v>
       </c>
       <c r="N95" s="4">
-        <f t="shared" si="1"/>
+        <f>M95/L95</f>
         <v>4.5049737057012065</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>10</v>
       </c>
@@ -4829,11 +4867,11 @@
         <v>393048055.903</v>
       </c>
       <c r="N96" s="4">
-        <f t="shared" si="1"/>
+        <f>M96/L96</f>
         <v>4.7221185113439654</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>10</v>
       </c>
@@ -4874,11 +4912,11 @@
         <v>414224432.10900003</v>
       </c>
       <c r="N97" s="4">
-        <f t="shared" si="1"/>
+        <f>M97/L97</f>
         <v>5.3782671319515201</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>10</v>
       </c>
@@ -4919,11 +4957,11 @@
         <v>393737908.79900002</v>
       </c>
       <c r="N98" s="4">
-        <f t="shared" si="1"/>
+        <f>M98/L98</f>
         <v>6.2345514360825725</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>10</v>
       </c>
@@ -4964,11 +5002,11 @@
         <v>353883653.55000001</v>
       </c>
       <c r="N99" s="4">
-        <f t="shared" si="1"/>
+        <f>M99/L99</f>
         <v>6.5431510244174538</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>10</v>
       </c>
@@ -5009,11 +5047,11 @@
         <v>415391574.89499998</v>
       </c>
       <c r="N100" s="4">
-        <f t="shared" si="1"/>
+        <f>M100/L100</f>
         <v>6.5144867212730988</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>10</v>
       </c>
@@ -5054,11 +5092,11 @@
         <v>415789940.82800001</v>
       </c>
       <c r="N101" s="4">
-        <f t="shared" si="1"/>
+        <f>M101/L101</f>
         <v>7.2537545600144258</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>10</v>
       </c>
@@ -5099,11 +5137,11 @@
         <v>469415595.53799999</v>
       </c>
       <c r="N102" s="4">
-        <f t="shared" si="1"/>
+        <f>M102/L102</f>
         <v>7.3096484642742601</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>10</v>
       </c>
@@ -5144,11 +5182,11 @@
         <v>397231991.88300002</v>
       </c>
       <c r="N103" s="4">
-        <f t="shared" si="1"/>
+        <f>M103/L103</f>
         <v>6.9656269590102893</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>10</v>
       </c>
@@ -5189,11 +5227,11 @@
         <v>445285847.11699998</v>
       </c>
       <c r="N104" s="4">
-        <f t="shared" si="1"/>
+        <f>M104/L104</f>
         <v>7.3040258733943917</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>10</v>
       </c>
@@ -5234,11 +5272,11 @@
         <v>442299074.23699999</v>
       </c>
       <c r="N105" s="4">
-        <f t="shared" si="1"/>
+        <f>M105/L105</f>
         <v>6.8335929229136507</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>10</v>
       </c>
@@ -5279,11 +5317,11 @@
         <v>414720198.32700002</v>
       </c>
       <c r="N106" s="4">
-        <f t="shared" si="1"/>
+        <f>M106/L106</f>
         <v>5.6025379777646682</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>10</v>
       </c>
@@ -5324,11 +5362,11 @@
         <v>517962778.70999998</v>
       </c>
       <c r="N107" s="4">
-        <f t="shared" si="1"/>
+        <f>M107/L107</f>
         <v>6.3024942868285825</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>10</v>
       </c>
@@ -5369,11 +5407,11 @@
         <v>497247306.19300002</v>
       </c>
       <c r="N108" s="4">
-        <f t="shared" si="1"/>
+        <f>M108/L108</f>
         <v>6.4024715488653374</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>10</v>
       </c>
@@ -5414,11 +5452,11 @@
         <v>602055475.83899999</v>
       </c>
       <c r="N109" s="4">
-        <f t="shared" si="1"/>
+        <f>M109/L109</f>
         <v>7.8297820199538046</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>10</v>
       </c>
@@ -5459,11 +5497,11 @@
         <v>489091678.54799998</v>
       </c>
       <c r="N110" s="4">
-        <f t="shared" si="1"/>
+        <f>M110/L110</f>
         <v>7.9221029501192035</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>10</v>
       </c>
@@ -5504,11 +5542,11 @@
         <v>433382634.366</v>
       </c>
       <c r="N111" s="4">
-        <f t="shared" si="1"/>
+        <f>M111/L111</f>
         <v>7.7768005829998934</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>10</v>
       </c>
@@ -5549,11 +5587,11 @@
         <v>492105870.87599999</v>
       </c>
       <c r="N112" s="4">
-        <f t="shared" si="1"/>
+        <f>M112/L112</f>
         <v>7.3204758522681628</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>10</v>
       </c>
@@ -5594,11 +5632,11 @@
         <v>526832884.82099998</v>
       </c>
       <c r="N113" s="4">
-        <f t="shared" si="1"/>
+        <f>M113/L113</f>
         <v>7.5883796207023595</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>10</v>
       </c>
@@ -5639,11 +5677,11 @@
         <v>459156829.39899999</v>
       </c>
       <c r="N114" s="4">
-        <f t="shared" si="1"/>
+        <f>M114/L114</f>
         <v>6.8247004284819566</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>10</v>
       </c>
@@ -5684,11 +5722,11 @@
         <v>409863216.77700001</v>
       </c>
       <c r="N115" s="4">
-        <f t="shared" si="1"/>
+        <f>M115/L115</f>
         <v>5.9980172831425209</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>10</v>
       </c>
@@ -5729,11 +5767,11 @@
         <v>438436308.60900003</v>
       </c>
       <c r="N116" s="4">
-        <f t="shared" si="1"/>
+        <f>M116/L116</f>
         <v>6.5413878095249522</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>10</v>
       </c>
@@ -5774,11 +5812,11 @@
         <v>399329584.24199998</v>
       </c>
       <c r="N117" s="4">
-        <f t="shared" si="1"/>
+        <f>M117/L117</f>
         <v>5.7868451733200548</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>10</v>
       </c>
@@ -5819,11 +5857,11 @@
         <v>399160312.78399998</v>
       </c>
       <c r="N118" s="4">
-        <f t="shared" si="1"/>
+        <f>M118/L118</f>
         <v>5.5140630709080103</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>10</v>
       </c>
@@ -5864,11 +5902,11 @@
         <v>439850462.70300001</v>
       </c>
       <c r="N119" s="4">
-        <f t="shared" si="1"/>
+        <f>M119/L119</f>
         <v>5.4186417477369853</v>
       </c>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>10</v>
       </c>
@@ -5909,11 +5947,11 @@
         <v>427101623.80400002</v>
       </c>
       <c r="N120" s="4">
-        <f t="shared" si="1"/>
+        <f>M120/L120</f>
         <v>5.9735292373633593</v>
       </c>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>10</v>
       </c>
@@ -5954,11 +5992,11 @@
         <v>460968888.54900002</v>
       </c>
       <c r="N121" s="4">
-        <f t="shared" si="1"/>
+        <f>M121/L121</f>
         <v>6.2206763509521981</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>10</v>
       </c>
@@ -5999,11 +6037,11 @@
         <v>375792108.57099998</v>
       </c>
       <c r="N122" s="4">
-        <f t="shared" si="1"/>
+        <f>M122/L122</f>
         <v>5.7517630001489088</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>10</v>
       </c>
@@ -6044,11 +6082,11 @@
         <v>337985407.57200003</v>
       </c>
       <c r="N123" s="4">
-        <f t="shared" si="1"/>
+        <f>M123/L123</f>
         <v>5.5567552201023025</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>10</v>
       </c>
@@ -6089,11 +6127,11 @@
         <v>404916171.85500002</v>
       </c>
       <c r="N124" s="4">
-        <f t="shared" si="1"/>
+        <f>M124/L124</f>
         <v>5.1949530250796903</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>10</v>
       </c>
@@ -6134,11 +6172,11 @@
         <v>349762731.222</v>
       </c>
       <c r="N125" s="4">
-        <f t="shared" si="1"/>
+        <f>M125/L125</f>
         <v>5.0570003495311893</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>10</v>
       </c>
@@ -6179,11 +6217,11 @@
         <v>360424705.426</v>
       </c>
       <c r="N126" s="4">
-        <f t="shared" si="1"/>
+        <f>M126/L126</f>
         <v>5.0841372745692679</v>
       </c>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>10</v>
       </c>
@@ -6224,11 +6262,11 @@
         <v>369759722.84799999</v>
       </c>
       <c r="N127" s="4">
-        <f t="shared" si="1"/>
+        <f>M127/L127</f>
         <v>5.2325660979614765</v>
       </c>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>10</v>
       </c>
@@ -6269,11 +6307,11 @@
         <v>368755770.94199997</v>
       </c>
       <c r="N128" s="4">
-        <f t="shared" si="1"/>
+        <f>M128/L128</f>
         <v>5.40834390113793</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>10</v>
       </c>
@@ -6314,11 +6352,11 @@
         <v>353992726.68599999</v>
       </c>
       <c r="N129" s="4">
-        <f t="shared" si="1"/>
+        <f>M129/L129</f>
         <v>5.2552355831117659</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>10</v>
       </c>
@@ -6359,11 +6397,11 @@
         <v>397807179.528</v>
       </c>
       <c r="N130" s="4">
-        <f t="shared" si="1"/>
+        <f>M130/L130</f>
         <v>5.0264001219252767</v>
       </c>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>10</v>
       </c>
@@ -6404,11 +6442,11 @@
         <v>431798659.278</v>
       </c>
       <c r="N131" s="4">
-        <f t="shared" ref="N131:N194" si="2">M131/L131</f>
+        <f>M131/L131</f>
         <v>5.0652666476200476</v>
       </c>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>10</v>
       </c>
@@ -6449,11 +6487,11 @@
         <v>397443755.81699997</v>
       </c>
       <c r="N132" s="4">
-        <f t="shared" si="2"/>
+        <f>M132/L132</f>
         <v>5.204850467999953</v>
       </c>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>10</v>
       </c>
@@ -6494,11 +6532,11 @@
         <v>455950175.25</v>
       </c>
       <c r="N133" s="4">
-        <f t="shared" si="2"/>
+        <f>M133/L133</f>
         <v>5.8787298153963503</v>
       </c>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>10</v>
       </c>
@@ -6539,11 +6577,11 @@
         <v>384334671.71399999</v>
       </c>
       <c r="N134" s="4">
-        <f t="shared" si="2"/>
+        <f>M134/L134</f>
         <v>6.2896380289479881</v>
       </c>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>10</v>
       </c>
@@ -6584,11 +6622,11 @@
         <v>386802724.14399999</v>
       </c>
       <c r="N135" s="4">
-        <f t="shared" si="2"/>
+        <f>M135/L135</f>
         <v>6.3962759408090015</v>
       </c>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>10</v>
       </c>
@@ -6629,11 +6667,11 @@
         <v>462102514.95499998</v>
       </c>
       <c r="N136" s="4">
-        <f t="shared" si="2"/>
+        <f>M136/L136</f>
         <v>6.9370958642733731</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>10</v>
       </c>
@@ -6674,11 +6712,11 @@
         <v>466330715.17900002</v>
       </c>
       <c r="N137" s="4">
-        <f t="shared" si="2"/>
+        <f>M137/L137</f>
         <v>6.9442657474978429</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>10</v>
       </c>
@@ -6719,11 +6757,11 @@
         <v>471389962.611</v>
       </c>
       <c r="N138" s="4">
-        <f t="shared" si="2"/>
+        <f>M138/L138</f>
         <v>7.3118105582621089</v>
       </c>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>10</v>
       </c>
@@ -6764,11 +6802,11 @@
         <v>467351629.88599998</v>
       </c>
       <c r="N139" s="4">
-        <f t="shared" si="2"/>
+        <f>M139/L139</f>
         <v>7.8656002724802061</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>10</v>
       </c>
@@ -6809,11 +6847,11 @@
         <v>457136103.80000001</v>
       </c>
       <c r="N140" s="4">
-        <f t="shared" si="2"/>
+        <f>M140/L140</f>
         <v>7.8525958586917852</v>
       </c>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>10</v>
       </c>
@@ -6854,11 +6892,11 @@
         <v>502188298.903</v>
       </c>
       <c r="N141" s="4">
-        <f t="shared" si="2"/>
+        <f>M141/L141</f>
         <v>7.0026522138755194</v>
       </c>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>10</v>
       </c>
@@ -6899,11 +6937,11 @@
         <v>544520723.64100003</v>
       </c>
       <c r="N142" s="4">
-        <f t="shared" si="2"/>
+        <f>M142/L142</f>
         <v>6.6299292502186065</v>
       </c>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>10</v>
       </c>
@@ -6944,11 +6982,11 @@
         <v>540739663.176</v>
       </c>
       <c r="N143" s="4">
-        <f t="shared" si="2"/>
+        <f>M143/L143</f>
         <v>7.3625508788337459</v>
       </c>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>10</v>
       </c>
@@ -6989,11 +7027,11 @@
         <v>575159653.98000002</v>
       </c>
       <c r="N144" s="4">
-        <f t="shared" si="2"/>
+        <f>M144/L144</f>
         <v>7.3380189204800095</v>
       </c>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>10</v>
       </c>
@@ -7034,11 +7072,11 @@
         <v>589260796.59099996</v>
       </c>
       <c r="N145" s="4">
-        <f t="shared" si="2"/>
+        <f>M145/L145</f>
         <v>8.0685814059008258</v>
       </c>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>10</v>
       </c>
@@ -7079,64 +7117,64 @@
         <v>489144168.71499997</v>
       </c>
       <c r="N146" s="4">
-        <f t="shared" si="2"/>
+        <f>M146/L146</f>
         <v>8.5010281337941347</v>
       </c>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.5">
-      <c r="A147" t="s">
-        <v>10</v>
-      </c>
-      <c r="B147">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A147" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B147" s="1">
+        <v>20170101</v>
+      </c>
+      <c r="C147" s="1">
+        <v>20170301</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G147" s="3">
+        <v>30214</v>
+      </c>
+      <c r="H147" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I147" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J147" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K147" t="s">
+        <v>18</v>
+      </c>
+      <c r="L147" s="1">
+        <v>57539413</v>
+      </c>
+      <c r="M147" s="1">
+        <v>489144169</v>
+      </c>
+      <c r="N147" s="4">
+        <f>M147/L147</f>
+        <v>8.5010281387472624</v>
+      </c>
+    </row>
+    <row r="148" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A148" t="s">
+        <v>10</v>
+      </c>
+      <c r="B148">
         <v>20170201</v>
       </c>
-      <c r="C147">
+      <c r="C148">
         <v>20170401</v>
-      </c>
-      <c r="D147" t="s">
-        <v>11</v>
-      </c>
-      <c r="E147" t="s">
-        <v>12</v>
-      </c>
-      <c r="F147" t="s">
-        <v>13</v>
-      </c>
-      <c r="G147" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H147" t="s">
-        <v>21</v>
-      </c>
-      <c r="I147" t="s">
-        <v>16</v>
-      </c>
-      <c r="J147" t="s">
-        <v>17</v>
-      </c>
-      <c r="K147" t="s">
-        <v>18</v>
-      </c>
-      <c r="L147">
-        <v>59283838</v>
-      </c>
-      <c r="M147">
-        <v>455889093.56400001</v>
-      </c>
-      <c r="N147" s="4">
-        <f t="shared" si="2"/>
-        <v>7.6899389267611182</v>
-      </c>
-    </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.5">
-      <c r="A148" t="s">
-        <v>10</v>
-      </c>
-      <c r="B148">
-        <v>20170301</v>
-      </c>
-      <c r="C148">
-        <v>20170501</v>
       </c>
       <c r="D148" t="s">
         <v>11</v>
@@ -7163,70 +7201,70 @@
         <v>18</v>
       </c>
       <c r="L148">
-        <v>74022585</v>
+        <v>59283838</v>
       </c>
       <c r="M148">
-        <v>534081328.389</v>
+        <v>455889093.56400001</v>
       </c>
       <c r="N148" s="4">
-        <f t="shared" si="2"/>
-        <v>7.2151131764582388</v>
-      </c>
-    </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.5">
-      <c r="A149" t="s">
-        <v>10</v>
-      </c>
-      <c r="B149">
+        <f>M148/L148</f>
+        <v>7.6899389267611182</v>
+      </c>
+    </row>
+    <row r="149" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A149" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B149" s="1">
+        <v>20170201</v>
+      </c>
+      <c r="C149" s="1">
         <v>20170401</v>
       </c>
-      <c r="C149">
-        <v>20170601</v>
-      </c>
-      <c r="D149" t="s">
-        <v>11</v>
-      </c>
-      <c r="E149" t="s">
-        <v>12</v>
-      </c>
-      <c r="F149" t="s">
-        <v>13</v>
-      </c>
-      <c r="G149" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H149" t="s">
+      <c r="D149" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G149" s="3">
+        <v>30214</v>
+      </c>
+      <c r="H149" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I149" t="s">
-        <v>16</v>
-      </c>
-      <c r="J149" t="s">
+      <c r="I149" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J149" s="1" t="s">
         <v>17</v>
       </c>
       <c r="K149" t="s">
         <v>18</v>
       </c>
-      <c r="L149">
-        <v>59946982</v>
-      </c>
-      <c r="M149">
-        <v>444118037.583</v>
+      <c r="L149" s="1">
+        <v>59283838</v>
+      </c>
+      <c r="M149" s="1">
+        <v>455889094</v>
       </c>
       <c r="N149" s="4">
-        <f t="shared" si="2"/>
-        <v>7.40851370270817</v>
-      </c>
-    </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.5">
+        <f>M149/L149</f>
+        <v>7.6899389341155677</v>
+      </c>
+    </row>
+    <row r="150" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>10</v>
       </c>
       <c r="B150">
+        <v>20170301</v>
+      </c>
+      <c r="C150">
         <v>20170501</v>
-      </c>
-      <c r="C150">
-        <v>20170701</v>
       </c>
       <c r="D150" t="s">
         <v>11</v>
@@ -7253,70 +7291,70 @@
         <v>18</v>
       </c>
       <c r="L150">
-        <v>59536287</v>
+        <v>74022585</v>
       </c>
       <c r="M150">
-        <v>487474912.67799997</v>
+        <v>534081328.389</v>
       </c>
       <c r="N150" s="4">
-        <f t="shared" si="2"/>
-        <v>8.1878621802196019</v>
-      </c>
-    </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.5">
-      <c r="A151" t="s">
-        <v>10</v>
-      </c>
-      <c r="B151">
+        <f>M150/L150</f>
+        <v>7.2151131764582388</v>
+      </c>
+    </row>
+    <row r="151" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A151" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B151" s="1">
+        <v>20170301</v>
+      </c>
+      <c r="C151" s="1">
+        <v>20170501</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G151" s="3">
+        <v>30214</v>
+      </c>
+      <c r="H151" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I151" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J151" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K151" t="s">
+        <v>18</v>
+      </c>
+      <c r="L151" s="1">
+        <v>74022585</v>
+      </c>
+      <c r="M151" s="1">
+        <v>534081328</v>
+      </c>
+      <c r="N151" s="4">
+        <f>M151/L151</f>
+        <v>7.215113171203086</v>
+      </c>
+    </row>
+    <row r="152" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A152" t="s">
+        <v>10</v>
+      </c>
+      <c r="B152">
+        <v>20170401</v>
+      </c>
+      <c r="C152">
         <v>20170601</v>
-      </c>
-      <c r="C151">
-        <v>20170801</v>
-      </c>
-      <c r="D151" t="s">
-        <v>11</v>
-      </c>
-      <c r="E151" t="s">
-        <v>12</v>
-      </c>
-      <c r="F151" t="s">
-        <v>13</v>
-      </c>
-      <c r="G151" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H151" t="s">
-        <v>21</v>
-      </c>
-      <c r="I151" t="s">
-        <v>16</v>
-      </c>
-      <c r="J151" t="s">
-        <v>17</v>
-      </c>
-      <c r="K151" t="s">
-        <v>18</v>
-      </c>
-      <c r="L151">
-        <v>60616969</v>
-      </c>
-      <c r="M151">
-        <v>491804010.87900001</v>
-      </c>
-      <c r="N151" s="4">
-        <f t="shared" si="2"/>
-        <v>8.1133058777485232</v>
-      </c>
-    </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.5">
-      <c r="A152" t="s">
-        <v>10</v>
-      </c>
-      <c r="B152">
-        <v>20170701</v>
-      </c>
-      <c r="C152">
-        <v>20170901</v>
       </c>
       <c r="D152" t="s">
         <v>11</v>
@@ -7343,70 +7381,70 @@
         <v>18</v>
       </c>
       <c r="L152">
-        <v>63170790</v>
+        <v>59946982</v>
       </c>
       <c r="M152">
-        <v>495517738.89499998</v>
+        <v>444118037.583</v>
       </c>
       <c r="N152" s="4">
-        <f t="shared" si="2"/>
-        <v>7.8440959642106733</v>
-      </c>
-    </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.5">
-      <c r="A153" t="s">
-        <v>10</v>
-      </c>
-      <c r="B153">
-        <v>20170801</v>
-      </c>
-      <c r="C153">
-        <v>20171001</v>
-      </c>
-      <c r="D153" t="s">
-        <v>11</v>
-      </c>
-      <c r="E153" t="s">
-        <v>12</v>
-      </c>
-      <c r="F153" t="s">
-        <v>13</v>
-      </c>
-      <c r="G153" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H153" t="s">
+        <f>M152/L152</f>
+        <v>7.40851370270817</v>
+      </c>
+    </row>
+    <row r="153" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A153" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B153" s="1">
+        <v>20170401</v>
+      </c>
+      <c r="C153" s="1">
+        <v>20170601</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G153" s="3">
+        <v>30214</v>
+      </c>
+      <c r="H153" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I153" t="s">
-        <v>16</v>
-      </c>
-      <c r="J153" t="s">
+      <c r="I153" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J153" s="1" t="s">
         <v>17</v>
       </c>
       <c r="K153" t="s">
         <v>18</v>
       </c>
-      <c r="L153">
-        <v>76499143</v>
-      </c>
-      <c r="M153">
-        <v>557634856.32299995</v>
+      <c r="L153" s="1">
+        <v>59946982</v>
+      </c>
+      <c r="M153" s="1">
+        <v>444118038</v>
       </c>
       <c r="N153" s="4">
-        <f t="shared" si="2"/>
-        <v>7.2894261877286644</v>
-      </c>
-    </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.5">
+        <f>M153/L153</f>
+        <v>7.4085137096643168</v>
+      </c>
+    </row>
+    <row r="154" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>10</v>
       </c>
       <c r="B154">
-        <v>20170901</v>
+        <v>20170501</v>
       </c>
       <c r="C154">
-        <v>20171101</v>
+        <v>20170701</v>
       </c>
       <c r="D154" t="s">
         <v>11</v>
@@ -7433,70 +7471,70 @@
         <v>18</v>
       </c>
       <c r="L154">
-        <v>81075389</v>
+        <v>59536287</v>
       </c>
       <c r="M154">
-        <v>574041990.64400005</v>
+        <v>487474912.67799997</v>
       </c>
       <c r="N154" s="4">
-        <f t="shared" si="2"/>
-        <v>7.0803482749123789</v>
-      </c>
-    </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.5">
-      <c r="A155" t="s">
-        <v>10</v>
-      </c>
-      <c r="B155">
-        <v>20171001</v>
-      </c>
-      <c r="C155">
-        <v>20171201</v>
-      </c>
-      <c r="D155" t="s">
-        <v>11</v>
-      </c>
-      <c r="E155" t="s">
-        <v>12</v>
-      </c>
-      <c r="F155" t="s">
-        <v>13</v>
-      </c>
-      <c r="G155" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H155" t="s">
+        <f>M154/L154</f>
+        <v>8.1878621802196019</v>
+      </c>
+    </row>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A155" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B155" s="1">
+        <v>20170501</v>
+      </c>
+      <c r="C155" s="1">
+        <v>20170701</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G155" s="3">
+        <v>30214</v>
+      </c>
+      <c r="H155" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I155" t="s">
-        <v>16</v>
-      </c>
-      <c r="J155" t="s">
+      <c r="I155" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J155" s="1" t="s">
         <v>17</v>
       </c>
       <c r="K155" t="s">
         <v>18</v>
       </c>
-      <c r="L155">
-        <v>81931953</v>
-      </c>
-      <c r="M155">
-        <v>559000757.50999999</v>
+      <c r="L155" s="1">
+        <v>59536287</v>
+      </c>
+      <c r="M155" s="1">
+        <v>487474913</v>
       </c>
       <c r="N155" s="4">
-        <f t="shared" si="2"/>
-        <v>6.8227442046938638</v>
-      </c>
-    </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.5">
+        <f>M155/L155</f>
+        <v>8.1878621856280684</v>
+      </c>
+    </row>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>10</v>
       </c>
       <c r="B156">
-        <v>20171101</v>
-      </c>
-      <c r="C156" s="1">
-        <v>20170101</v>
+        <v>20170601</v>
+      </c>
+      <c r="C156">
+        <v>20170801</v>
       </c>
       <c r="D156" t="s">
         <v>11</v>
@@ -7523,115 +7561,115 @@
         <v>18</v>
       </c>
       <c r="L156">
-        <v>84977607</v>
+        <v>60616969</v>
       </c>
       <c r="M156">
-        <v>524085734.76599997</v>
+        <v>491804010.87900001</v>
       </c>
       <c r="N156" s="4">
-        <f t="shared" si="2"/>
-        <v>6.1673392940566094</v>
-      </c>
-    </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.5">
-      <c r="A157" t="s">
-        <v>10</v>
-      </c>
-      <c r="B157">
-        <v>20171201</v>
+        <f>M156/L156</f>
+        <v>8.1133058777485232</v>
+      </c>
+    </row>
+    <row r="157" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A157" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B157" s="1">
+        <v>20170601</v>
       </c>
       <c r="C157" s="1">
-        <v>20170201</v>
-      </c>
-      <c r="D157" t="s">
-        <v>11</v>
-      </c>
-      <c r="E157" t="s">
-        <v>12</v>
-      </c>
-      <c r="F157" t="s">
-        <v>13</v>
-      </c>
-      <c r="G157" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H157" t="s">
+        <v>20170801</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G157" s="3">
+        <v>30214</v>
+      </c>
+      <c r="H157" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I157" t="s">
-        <v>16</v>
-      </c>
-      <c r="J157" t="s">
+      <c r="I157" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J157" s="1" t="s">
         <v>17</v>
       </c>
       <c r="K157" t="s">
         <v>18</v>
       </c>
-      <c r="L157">
-        <v>82294638</v>
-      </c>
-      <c r="M157">
-        <v>531476392.083</v>
+      <c r="L157" s="1">
+        <v>60616969</v>
+      </c>
+      <c r="M157" s="1">
+        <v>491804011</v>
       </c>
       <c r="N157" s="4">
-        <f t="shared" si="2"/>
-        <v>6.4582141072544728</v>
-      </c>
-    </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.5">
-      <c r="A158" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B158" s="1">
-        <v>20170101</v>
-      </c>
-      <c r="C158" s="1">
-        <v>20170301</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E158" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F158" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G158" s="3">
-        <v>30214</v>
-      </c>
-      <c r="H158" s="1" t="s">
+        <f>M157/L157</f>
+        <v>8.1133058797446633</v>
+      </c>
+    </row>
+    <row r="158" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A158" t="s">
+        <v>10</v>
+      </c>
+      <c r="B158">
+        <v>20170701</v>
+      </c>
+      <c r="C158">
+        <v>20170901</v>
+      </c>
+      <c r="D158" t="s">
+        <v>11</v>
+      </c>
+      <c r="E158" t="s">
+        <v>12</v>
+      </c>
+      <c r="F158" t="s">
+        <v>13</v>
+      </c>
+      <c r="G158" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H158" t="s">
         <v>21</v>
       </c>
-      <c r="I158" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J158" s="1" t="s">
+      <c r="I158" t="s">
+        <v>16</v>
+      </c>
+      <c r="J158" t="s">
         <v>17</v>
       </c>
       <c r="K158" t="s">
         <v>18</v>
       </c>
-      <c r="L158" s="1">
-        <v>57539413</v>
-      </c>
-      <c r="M158" s="1">
-        <v>489144169</v>
+      <c r="L158">
+        <v>63170790</v>
+      </c>
+      <c r="M158">
+        <v>495517738.89499998</v>
       </c>
       <c r="N158" s="4">
-        <f t="shared" si="2"/>
-        <v>8.5010281387472624</v>
-      </c>
-    </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.5">
+        <f>M158/L158</f>
+        <v>7.8440959642106733</v>
+      </c>
+    </row>
+    <row r="159" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B159" s="1">
-        <v>20170201</v>
+        <v>20170701</v>
       </c>
       <c r="C159" s="1">
-        <v>20170401</v>
+        <v>20170901</v>
       </c>
       <c r="D159" s="1" t="s">
         <v>11</v>
@@ -7658,70 +7696,70 @@
         <v>18</v>
       </c>
       <c r="L159" s="1">
-        <v>59283838</v>
+        <v>63170790</v>
       </c>
       <c r="M159" s="1">
-        <v>455889094</v>
+        <v>495517739</v>
       </c>
       <c r="N159" s="4">
-        <f t="shared" si="2"/>
-        <v>7.6899389341155677</v>
-      </c>
-    </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.5">
-      <c r="A160" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B160" s="1">
-        <v>20170301</v>
-      </c>
-      <c r="C160" s="1">
-        <v>20170501</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E160" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F160" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G160" s="3">
-        <v>30214</v>
-      </c>
-      <c r="H160" s="1" t="s">
+        <f>M159/L159</f>
+        <v>7.8440959658728344</v>
+      </c>
+    </row>
+    <row r="160" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A160" t="s">
+        <v>10</v>
+      </c>
+      <c r="B160">
+        <v>20170801</v>
+      </c>
+      <c r="C160">
+        <v>20171001</v>
+      </c>
+      <c r="D160" t="s">
+        <v>11</v>
+      </c>
+      <c r="E160" t="s">
+        <v>12</v>
+      </c>
+      <c r="F160" t="s">
+        <v>13</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H160" t="s">
         <v>21</v>
       </c>
-      <c r="I160" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J160" s="1" t="s">
+      <c r="I160" t="s">
+        <v>16</v>
+      </c>
+      <c r="J160" t="s">
         <v>17</v>
       </c>
       <c r="K160" t="s">
         <v>18</v>
       </c>
-      <c r="L160" s="1">
-        <v>74022585</v>
-      </c>
-      <c r="M160" s="1">
-        <v>534081328</v>
+      <c r="L160">
+        <v>76499143</v>
+      </c>
+      <c r="M160">
+        <v>557634856.32299995</v>
       </c>
       <c r="N160" s="4">
-        <f t="shared" si="2"/>
-        <v>7.215113171203086</v>
-      </c>
-    </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.5">
+        <f>M160/L160</f>
+        <v>7.2894261877286644</v>
+      </c>
+    </row>
+    <row r="161" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B161" s="1">
-        <v>20170401</v>
+        <v>20170801</v>
       </c>
       <c r="C161" s="1">
-        <v>20170601</v>
+        <v>20171001</v>
       </c>
       <c r="D161" s="1" t="s">
         <v>11</v>
@@ -7748,70 +7786,70 @@
         <v>18</v>
       </c>
       <c r="L161" s="1">
-        <v>59946982</v>
+        <v>76499143</v>
       </c>
       <c r="M161" s="1">
-        <v>444118038</v>
+        <v>557634856</v>
       </c>
       <c r="N161" s="4">
-        <f t="shared" si="2"/>
-        <v>7.4085137096643168</v>
-      </c>
-    </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.5">
-      <c r="A162" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B162" s="1">
-        <v>20170501</v>
-      </c>
-      <c r="C162" s="1">
-        <v>20170701</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E162" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F162" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G162" s="3">
-        <v>30214</v>
-      </c>
-      <c r="H162" s="1" t="s">
+        <f>M161/L161</f>
+        <v>7.2894261835063956</v>
+      </c>
+    </row>
+    <row r="162" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A162" t="s">
+        <v>10</v>
+      </c>
+      <c r="B162">
+        <v>20170901</v>
+      </c>
+      <c r="C162">
+        <v>20171101</v>
+      </c>
+      <c r="D162" t="s">
+        <v>11</v>
+      </c>
+      <c r="E162" t="s">
+        <v>12</v>
+      </c>
+      <c r="F162" t="s">
+        <v>13</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H162" t="s">
         <v>21</v>
       </c>
-      <c r="I162" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J162" s="1" t="s">
+      <c r="I162" t="s">
+        <v>16</v>
+      </c>
+      <c r="J162" t="s">
         <v>17</v>
       </c>
       <c r="K162" t="s">
         <v>18</v>
       </c>
-      <c r="L162" s="1">
-        <v>59536287</v>
-      </c>
-      <c r="M162" s="1">
-        <v>487474913</v>
+      <c r="L162">
+        <v>81075389</v>
+      </c>
+      <c r="M162">
+        <v>574041990.64400005</v>
       </c>
       <c r="N162" s="4">
-        <f t="shared" si="2"/>
-        <v>8.1878621856280684</v>
-      </c>
-    </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.5">
+        <f>M162/L162</f>
+        <v>7.0803482749123789</v>
+      </c>
+    </row>
+    <row r="163" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B163" s="1">
-        <v>20170601</v>
+        <v>20170901</v>
       </c>
       <c r="C163" s="1">
-        <v>20170801</v>
+        <v>20171101</v>
       </c>
       <c r="D163" s="1" t="s">
         <v>11</v>
@@ -7838,70 +7876,70 @@
         <v>18</v>
       </c>
       <c r="L163" s="1">
-        <v>60616969</v>
+        <v>81075389</v>
       </c>
       <c r="M163" s="1">
-        <v>491804011</v>
+        <v>574041991</v>
       </c>
       <c r="N163" s="4">
-        <f t="shared" si="2"/>
-        <v>8.1133058797446633</v>
-      </c>
-    </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.5">
-      <c r="A164" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B164" s="1">
-        <v>20170701</v>
-      </c>
-      <c r="C164" s="1">
-        <v>20170901</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E164" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F164" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G164" s="3">
-        <v>30214</v>
-      </c>
-      <c r="H164" s="1" t="s">
+        <f>M163/L163</f>
+        <v>7.0803482793033528</v>
+      </c>
+    </row>
+    <row r="164" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A164" t="s">
+        <v>10</v>
+      </c>
+      <c r="B164">
+        <v>20171001</v>
+      </c>
+      <c r="C164">
+        <v>20171201</v>
+      </c>
+      <c r="D164" t="s">
+        <v>11</v>
+      </c>
+      <c r="E164" t="s">
+        <v>12</v>
+      </c>
+      <c r="F164" t="s">
+        <v>13</v>
+      </c>
+      <c r="G164" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H164" t="s">
         <v>21</v>
       </c>
-      <c r="I164" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J164" s="1" t="s">
+      <c r="I164" t="s">
+        <v>16</v>
+      </c>
+      <c r="J164" t="s">
         <v>17</v>
       </c>
       <c r="K164" t="s">
         <v>18</v>
       </c>
-      <c r="L164" s="1">
-        <v>63170790</v>
-      </c>
-      <c r="M164" s="1">
-        <v>495517739</v>
+      <c r="L164">
+        <v>81931953</v>
+      </c>
+      <c r="M164">
+        <v>559000757.50999999</v>
       </c>
       <c r="N164" s="4">
-        <f t="shared" si="2"/>
-        <v>7.8440959658728344</v>
-      </c>
-    </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.5">
+        <f>M164/L164</f>
+        <v>6.8227442046938638</v>
+      </c>
+    </row>
+    <row r="165" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B165" s="1">
-        <v>20170801</v>
+        <v>20171001</v>
       </c>
       <c r="C165" s="1">
-        <v>20171001</v>
+        <v>20171201</v>
       </c>
       <c r="D165" s="1" t="s">
         <v>11</v>
@@ -7928,70 +7966,70 @@
         <v>18</v>
       </c>
       <c r="L165" s="1">
-        <v>76499143</v>
+        <v>81931953</v>
       </c>
       <c r="M165" s="1">
-        <v>557634856</v>
+        <v>559000758</v>
       </c>
       <c r="N165" s="4">
-        <f t="shared" si="2"/>
-        <v>7.2894261835063956</v>
-      </c>
-    </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.5">
-      <c r="A166" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B166" s="1">
-        <v>20170901</v>
+        <f>M165/L165</f>
+        <v>6.8227442106744363</v>
+      </c>
+    </row>
+    <row r="166" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A166" t="s">
+        <v>10</v>
+      </c>
+      <c r="B166">
+        <v>20171101</v>
       </c>
       <c r="C166" s="1">
+        <v>20170101</v>
+      </c>
+      <c r="D166" t="s">
+        <v>11</v>
+      </c>
+      <c r="E166" t="s">
+        <v>12</v>
+      </c>
+      <c r="F166" t="s">
+        <v>13</v>
+      </c>
+      <c r="G166" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H166" t="s">
+        <v>21</v>
+      </c>
+      <c r="I166" t="s">
+        <v>16</v>
+      </c>
+      <c r="J166" t="s">
+        <v>17</v>
+      </c>
+      <c r="K166" t="s">
+        <v>18</v>
+      </c>
+      <c r="L166">
+        <v>84977607</v>
+      </c>
+      <c r="M166">
+        <v>524085734.76599997</v>
+      </c>
+      <c r="N166" s="4">
+        <f>M166/L166</f>
+        <v>6.1673392940566094</v>
+      </c>
+    </row>
+    <row r="167" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A167" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B167" s="1">
         <v>20171101</v>
       </c>
-      <c r="D166" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E166" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F166" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G166" s="3">
-        <v>30214</v>
-      </c>
-      <c r="H166" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I166" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J166" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K166" t="s">
-        <v>18</v>
-      </c>
-      <c r="L166" s="1">
-        <v>81075389</v>
-      </c>
-      <c r="M166" s="1">
-        <v>574041991</v>
-      </c>
-      <c r="N166" s="4">
-        <f t="shared" si="2"/>
-        <v>7.0803482793033528</v>
-      </c>
-    </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.5">
-      <c r="A167" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B167" s="1">
-        <v>20171001</v>
-      </c>
-      <c r="C167" s="1">
-        <v>20171201</v>
+      <c r="C167">
+        <v>20180101</v>
       </c>
       <c r="D167" s="1" t="s">
         <v>11</v>
@@ -8018,62 +8056,62 @@
         <v>18</v>
       </c>
       <c r="L167" s="1">
-        <v>81931953</v>
+        <v>84977607</v>
       </c>
       <c r="M167" s="1">
-        <v>559000758</v>
+        <v>524085735</v>
       </c>
       <c r="N167" s="4">
-        <f t="shared" si="2"/>
-        <v>6.8227442106744363</v>
-      </c>
-    </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.5">
-      <c r="A168" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B168" s="1">
-        <v>20171101</v>
-      </c>
-      <c r="C168">
-        <v>20180101</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E168" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F168" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G168" s="3">
-        <v>30214</v>
-      </c>
-      <c r="H168" s="1" t="s">
+        <f>M167/L167</f>
+        <v>6.167339296810276</v>
+      </c>
+    </row>
+    <row r="168" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A168" t="s">
+        <v>10</v>
+      </c>
+      <c r="B168">
+        <v>20171201</v>
+      </c>
+      <c r="C168" s="1">
+        <v>20170201</v>
+      </c>
+      <c r="D168" t="s">
+        <v>11</v>
+      </c>
+      <c r="E168" t="s">
+        <v>12</v>
+      </c>
+      <c r="F168" t="s">
+        <v>13</v>
+      </c>
+      <c r="G168" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H168" t="s">
         <v>21</v>
       </c>
-      <c r="I168" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J168" s="1" t="s">
+      <c r="I168" t="s">
+        <v>16</v>
+      </c>
+      <c r="J168" t="s">
         <v>17</v>
       </c>
       <c r="K168" t="s">
         <v>18</v>
       </c>
-      <c r="L168" s="1">
-        <v>84977607</v>
-      </c>
-      <c r="M168" s="1">
-        <v>524085735</v>
+      <c r="L168">
+        <v>82294638</v>
+      </c>
+      <c r="M168">
+        <v>531476392.083</v>
       </c>
       <c r="N168" s="4">
-        <f t="shared" si="2"/>
-        <v>6.167339296810276</v>
-      </c>
-    </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.5">
+        <f>M168/L168</f>
+        <v>6.4582141072544728</v>
+      </c>
+    </row>
+    <row r="169" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
         <v>10</v>
       </c>
@@ -8114,11 +8152,11 @@
         <v>531476392</v>
       </c>
       <c r="N169" s="4">
-        <f t="shared" si="2"/>
+        <f>M169/L169</f>
         <v>6.4582141062459018</v>
       </c>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="170" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>10</v>
       </c>
@@ -8159,11 +8197,11 @@
         <v>523874163.403</v>
       </c>
       <c r="N170" s="4">
-        <f t="shared" si="2"/>
+        <f>M170/L170</f>
         <v>7.2036352142192994</v>
       </c>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="171" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>10</v>
       </c>
@@ -8204,11 +8242,11 @@
         <v>467731118.52399999</v>
       </c>
       <c r="N171" s="4">
-        <f t="shared" si="2"/>
+        <f>M171/L171</f>
         <v>7.4505849932773174</v>
       </c>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="172" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>10</v>
       </c>
@@ -8249,11 +8287,11 @@
         <v>623494996.454</v>
       </c>
       <c r="N172" s="4">
-        <f t="shared" si="2"/>
+        <f>M172/L172</f>
         <v>8.6845957318052189</v>
       </c>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="173" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>10</v>
       </c>
@@ -8294,11 +8332,11 @@
         <v>533771142.96899998</v>
       </c>
       <c r="N173" s="4">
-        <f t="shared" si="2"/>
+        <f>M173/L173</f>
         <v>8.7364201794031988</v>
       </c>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="174" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>10</v>
       </c>
@@ -8339,11 +8377,11 @@
         <v>606855489.53600001</v>
       </c>
       <c r="N174" s="4">
-        <f t="shared" si="2"/>
+        <f>M174/L174</f>
         <v>9.0332192391226833</v>
       </c>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="175" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>10</v>
       </c>
@@ -8384,11 +8422,11 @@
         <v>541150835.22000003</v>
       </c>
       <c r="N175" s="4">
-        <f t="shared" si="2"/>
+        <f>M175/L175</f>
         <v>7.6148956052403687</v>
       </c>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="176" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>10</v>
       </c>
@@ -8429,11 +8467,11 @@
         <v>517891569.028</v>
       </c>
       <c r="N176" s="4">
-        <f t="shared" si="2"/>
+        <f>M176/L176</f>
         <v>6.9377191393835647</v>
       </c>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>10</v>
       </c>
@@ -8474,11 +8512,11 @@
         <v>561054000.74800003</v>
       </c>
       <c r="N177" s="4">
-        <f t="shared" si="2"/>
+        <f>M177/L177</f>
         <v>6.6691154277940479</v>
       </c>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>10</v>
       </c>
@@ -8519,11 +8557,11 @@
         <v>550559323.28799999</v>
       </c>
       <c r="N178" s="4">
-        <f t="shared" si="2"/>
+        <f>M178/L178</f>
         <v>7.3887457101310545</v>
       </c>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="179" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>10</v>
       </c>
@@ -8564,11 +8602,11 @@
         <v>617283571.49100006</v>
       </c>
       <c r="N179" s="4">
-        <f t="shared" si="2"/>
+        <f>M179/L179</f>
         <v>7.0739153698040109</v>
       </c>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="180" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>10</v>
       </c>
@@ -8609,11 +8647,11 @@
         <v>564199767.84000003</v>
       </c>
       <c r="N180" s="4">
-        <f t="shared" si="2"/>
+        <f>M180/L180</f>
         <v>6.6208799479304314</v>
       </c>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="181" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>10</v>
       </c>
@@ -8654,11 +8692,11 @@
         <v>542441686.61600006</v>
       </c>
       <c r="N181" s="4">
-        <f t="shared" si="2"/>
+        <f>M181/L181</f>
         <v>6.92867724812199</v>
       </c>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="182" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>10</v>
       </c>
@@ -8699,11 +8737,11 @@
         <v>522076419.73799998</v>
       </c>
       <c r="N182" s="4">
-        <f t="shared" si="2"/>
+        <f>M182/L182</f>
         <v>7.2993637080272524</v>
       </c>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="183" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>10</v>
       </c>
@@ -8744,11 +8782,11 @@
         <v>462005217.83099997</v>
       </c>
       <c r="N183" s="4">
-        <f t="shared" si="2"/>
+        <f>M183/L183</f>
         <v>6.8616717572072092</v>
       </c>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="184" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>10</v>
       </c>
@@ -8789,11 +8827,11 @@
         <v>543042213.90499997</v>
       </c>
       <c r="N184" s="4">
-        <f t="shared" si="2"/>
+        <f>M184/L184</f>
         <v>7.9954218196504092</v>
       </c>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="185" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>10</v>
       </c>
@@ -8834,11 +8872,11 @@
         <v>571821538.301</v>
       </c>
       <c r="N185" s="4">
-        <f t="shared" si="2"/>
+        <f>M185/L185</f>
         <v>7.9853082886137532</v>
       </c>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="186" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>10</v>
       </c>
@@ -8879,11 +8917,11 @@
         <v>537176465.38499999</v>
       </c>
       <c r="N186" s="4">
-        <f t="shared" si="2"/>
+        <f>M186/L186</f>
         <v>7.1067332087968857</v>
       </c>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="187" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>10</v>
       </c>
@@ -8924,11 +8962,11 @@
         <v>503402292.162</v>
       </c>
       <c r="N187" s="4">
-        <f t="shared" si="2"/>
+        <f>M187/L187</f>
         <v>7.3837457648272427</v>
       </c>
     </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="188" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>10</v>
       </c>
@@ -8969,11 +9007,11 @@
         <v>530081935.27999997</v>
       </c>
       <c r="N188" s="4">
-        <f t="shared" si="2"/>
+        <f>M188/L188</f>
         <v>6.9225940926672704</v>
       </c>
     </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="189" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>10</v>
       </c>
@@ -9014,11 +9052,11 @@
         <v>532305077.84899998</v>
       </c>
       <c r="N189" s="4">
-        <f t="shared" si="2"/>
+        <f>M189/L189</f>
         <v>6.0493149571186864</v>
       </c>
     </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="190" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>10</v>
       </c>
@@ -9059,11 +9097,11 @@
         <v>500178953.35699999</v>
       </c>
       <c r="N190" s="4">
-        <f t="shared" si="2"/>
+        <f>M190/L190</f>
         <v>5.5299471550187684</v>
       </c>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="191" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>10</v>
       </c>
@@ -9104,11 +9142,11 @@
         <v>549237581.73899996</v>
       </c>
       <c r="N191" s="4">
-        <f t="shared" si="2"/>
+        <f>M191/L191</f>
         <v>5.6694577587253994</v>
       </c>
     </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="192" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>10</v>
       </c>
@@ -9149,11 +9187,11 @@
         <v>578534041.31400001</v>
       </c>
       <c r="N192" s="4">
-        <f t="shared" si="2"/>
+        <f>M192/L192</f>
         <v>6.4535455535166451</v>
       </c>
     </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="193" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>10</v>
       </c>
@@ -9194,11 +9232,11 @@
         <v>588432430.23199999</v>
       </c>
       <c r="N193" s="4">
-        <f t="shared" si="2"/>
+        <f>M193/L193</f>
         <v>7.7778661060743328</v>
       </c>
     </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="194" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>10</v>
       </c>
@@ -9239,11 +9277,11 @@
         <v>602139343.82500005</v>
       </c>
       <c r="N194" s="4">
-        <f t="shared" si="2"/>
+        <f>M194/L194</f>
         <v>8.4391591007328568</v>
       </c>
     </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="195" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>10</v>
       </c>
@@ -9284,11 +9322,11 @@
         <v>474331322.67799997</v>
       </c>
       <c r="N195" s="4">
-        <f t="shared" ref="N195:N258" si="3">M195/L195</f>
+        <f>M195/L195</f>
         <v>7.2840213035338097</v>
       </c>
     </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="196" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>10</v>
       </c>
@@ -9329,11 +9367,11 @@
         <v>428704760.58999997</v>
       </c>
       <c r="N196" s="4">
-        <f t="shared" si="3"/>
+        <f>M196/L196</f>
         <v>6.211715646522153</v>
       </c>
     </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="197" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>10</v>
       </c>
@@ -9374,11 +9412,11 @@
         <v>366986673.50999999</v>
       </c>
       <c r="N197" s="4">
-        <f t="shared" si="3"/>
+        <f>M197/L197</f>
         <v>5.4827820722650937</v>
       </c>
     </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="198" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>10</v>
       </c>
@@ -9419,11 +9457,11 @@
         <v>403351203.50700003</v>
       </c>
       <c r="N198" s="4">
-        <f t="shared" si="3"/>
+        <f>M198/L198</f>
         <v>6.004786180779508</v>
       </c>
     </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="199" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>10</v>
       </c>
@@ -9464,11 +9502,11 @@
         <v>452022203.60299999</v>
       </c>
       <c r="N199" s="4">
-        <f t="shared" si="3"/>
+        <f>M199/L199</f>
         <v>6.7844714798806551</v>
       </c>
     </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="200" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>10</v>
       </c>
@@ -9509,11 +9547,11 @@
         <v>459464994.45300001</v>
       </c>
       <c r="N200" s="4">
-        <f t="shared" si="3"/>
+        <f>M200/L200</f>
         <v>5.8534379140579782</v>
       </c>
     </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="201" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>10</v>
       </c>
@@ -9554,11 +9592,11 @@
         <v>441131177.34399998</v>
       </c>
       <c r="N201" s="4">
-        <f t="shared" si="3"/>
+        <f>M201/L201</f>
         <v>5.6648057043990452</v>
       </c>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="202" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>10</v>
       </c>
@@ -9599,11 +9637,11 @@
         <v>501810835.07800001</v>
       </c>
       <c r="N202" s="4">
-        <f t="shared" si="3"/>
+        <f>M202/L202</f>
         <v>5.4185916945645767</v>
       </c>
     </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="203" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>10</v>
       </c>
@@ -9644,11 +9682,11 @@
         <v>519187884.25999999</v>
       </c>
       <c r="N203" s="4">
-        <f t="shared" si="3"/>
+        <f>M203/L203</f>
         <v>5.2307687187935477</v>
       </c>
     </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="204" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>10</v>
       </c>
@@ -9689,11 +9727,11 @@
         <v>464093730.65100002</v>
       </c>
       <c r="N204" s="4">
-        <f t="shared" si="3"/>
+        <f>M204/L204</f>
         <v>5.2586344993314613</v>
       </c>
     </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="205" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>10</v>
       </c>
@@ -9734,11 +9772,11 @@
         <v>524398147.68800002</v>
       </c>
       <c r="N205" s="4">
-        <f t="shared" si="3"/>
+        <f>M205/L205</f>
         <v>5.4703566510717136</v>
       </c>
     </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="206" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>10</v>
       </c>
@@ -9779,11 +9817,11 @@
         <v>442051795.86900002</v>
       </c>
       <c r="N206" s="4">
-        <f t="shared" si="3"/>
+        <f>M206/L206</f>
         <v>5.7206951946006175</v>
       </c>
     </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="207" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>10</v>
       </c>
@@ -9824,11 +9862,11 @@
         <v>450576690.60000002</v>
       </c>
       <c r="N207" s="4">
-        <f t="shared" si="3"/>
+        <f>M207/L207</f>
         <v>6.0177687299118539</v>
       </c>
     </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="208" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>10</v>
       </c>
@@ -9869,11 +9907,11 @@
         <v>610739776.40999997</v>
       </c>
       <c r="N208" s="4">
-        <f t="shared" si="3"/>
+        <f>M208/L208</f>
         <v>7.3005091735855014</v>
       </c>
     </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="209" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>10</v>
       </c>
@@ -9914,11 +9952,11 @@
         <v>493230150.25599998</v>
       </c>
       <c r="N209" s="4">
-        <f t="shared" si="3"/>
+        <f>M209/L209</f>
         <v>7.542898534488498</v>
       </c>
     </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="210" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>10</v>
       </c>
@@ -9959,11 +9997,11 @@
         <v>505088092.61400002</v>
       </c>
       <c r="N210" s="4">
-        <f t="shared" si="3"/>
+        <f>M210/L210</f>
         <v>8.0297427764274705</v>
       </c>
     </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="211" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>10</v>
       </c>
@@ -10004,11 +10042,11 @@
         <v>554064772.51800001</v>
       </c>
       <c r="N211" s="4">
-        <f t="shared" si="3"/>
+        <f>M211/L211</f>
         <v>7.0712771413152815</v>
       </c>
     </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="212" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>10</v>
       </c>
@@ -10049,11 +10087,11 @@
         <v>594907083.42299998</v>
       </c>
       <c r="N212" s="4">
-        <f t="shared" si="3"/>
+        <f>M212/L212</f>
         <v>7.1390506270505476</v>
       </c>
     </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="213" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>10</v>
       </c>
@@ -10094,11 +10132,11 @@
         <v>605986469.43900001</v>
       </c>
       <c r="N213" s="4">
-        <f t="shared" si="3"/>
+        <f>M213/L213</f>
         <v>6.4171756665452637</v>
       </c>
     </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="214" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>10</v>
       </c>
@@ -10139,11 +10177,11 @@
         <v>695154804.88</v>
       </c>
       <c r="N214" s="4">
-        <f t="shared" si="3"/>
+        <f>M214/L214</f>
         <v>6.1303767835015899</v>
       </c>
     </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="215" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>10</v>
       </c>
@@ -10184,11 +10222,11 @@
         <v>715928997.08599997</v>
       </c>
       <c r="N215" s="4">
-        <f t="shared" si="3"/>
+        <f>M215/L215</f>
         <v>6.7888126519111918</v>
       </c>
     </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="216" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>10</v>
       </c>
@@ -10229,11 +10267,11 @@
         <v>695486304.11000001</v>
       </c>
       <c r="N216" s="4">
-        <f t="shared" si="3"/>
+        <f>M216/L216</f>
         <v>6.6399643899000864</v>
       </c>
     </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="217" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>10</v>
       </c>
@@ -10274,11 +10312,11 @@
         <v>731632411.204</v>
       </c>
       <c r="N217" s="4">
-        <f t="shared" si="3"/>
+        <f>M217/L217</f>
         <v>7.5486645331938176</v>
       </c>
     </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="218" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>10</v>
       </c>
@@ -10319,11 +10357,11 @@
         <v>590420779.551</v>
       </c>
       <c r="N218" s="4">
-        <f t="shared" si="3"/>
+        <f>M218/L218</f>
         <v>8.0013540507489154</v>
       </c>
     </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="219" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>10</v>
       </c>
@@ -10364,11 +10402,11 @@
         <v>645733220.32000005</v>
       </c>
       <c r="N219" s="4">
-        <f t="shared" si="3"/>
+        <f>M219/L219</f>
         <v>9.2677944996625126</v>
       </c>
     </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="220" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>10</v>
       </c>
@@ -10409,11 +10447,11 @@
         <v>701388943.13999999</v>
       </c>
       <c r="N220" s="4">
-        <f t="shared" si="3"/>
+        <f>M220/L220</f>
         <v>9.2955065608107272</v>
       </c>
     </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="221" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>10</v>
       </c>
@@ -10454,11 +10492,11 @@
         <v>678253495.37300003</v>
       </c>
       <c r="N221" s="4">
-        <f t="shared" si="3"/>
+        <f>M221/L221</f>
         <v>10.921722184203714</v>
       </c>
     </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="222" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>10</v>
       </c>
@@ -10499,11 +10537,11 @@
         <v>644773516.926</v>
       </c>
       <c r="N222" s="4">
-        <f t="shared" si="3"/>
+        <f>M222/L222</f>
         <v>10.245708911585641</v>
       </c>
     </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="223" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>10</v>
       </c>
@@ -10544,11 +10582,11 @@
         <v>663671830.20599997</v>
       </c>
       <c r="N223" s="4">
-        <f t="shared" si="3"/>
+        <f>M223/L223</f>
         <v>9.8962333609401796</v>
       </c>
     </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="224" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>10</v>
       </c>
@@ -10589,11 +10627,11 @@
         <v>650190741.29999995</v>
       </c>
       <c r="N224" s="4">
-        <f t="shared" si="3"/>
+        <f>M224/L224</f>
         <v>8.3929281190072711</v>
       </c>
     </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="225" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>10</v>
       </c>
@@ -10634,11 +10672,11 @@
         <v>686988973.148</v>
       </c>
       <c r="N225" s="4">
-        <f t="shared" si="3"/>
+        <f>M225/L225</f>
         <v>7.1568549972901438</v>
       </c>
     </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="226" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>10</v>
       </c>
@@ -10679,11 +10717,11 @@
         <v>705450064.41400003</v>
       </c>
       <c r="N226" s="4">
-        <f t="shared" si="3"/>
+        <f>M226/L226</f>
         <v>6.2179462951060751</v>
       </c>
     </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="227" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>10</v>
       </c>
@@ -10724,11 +10762,11 @@
         <v>711007956.09599996</v>
       </c>
       <c r="N227" s="4">
-        <f t="shared" si="3"/>
+        <f>M227/L227</f>
         <v>6.7204498542798756</v>
       </c>
     </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="228" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>10</v>
       </c>
@@ -10769,11 +10807,11 @@
         <v>720435107.84500003</v>
       </c>
       <c r="N228" s="4">
-        <f t="shared" si="3"/>
+        <f>M228/L228</f>
         <v>7.1816226074058562</v>
       </c>
     </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="229" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>10</v>
       </c>
@@ -10814,11 +10852,11 @@
         <v>729347240.09300005</v>
       </c>
       <c r="N229" s="4">
-        <f t="shared" si="3"/>
+        <f>M229/L229</f>
         <v>7.9831984761451968</v>
       </c>
     </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="230" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>10</v>
       </c>
@@ -10859,11 +10897,11 @@
         <v>635435086.10800004</v>
       </c>
       <c r="N230" s="4">
-        <f t="shared" si="3"/>
+        <f>M230/L230</f>
         <v>9.3421774508754893</v>
       </c>
     </row>
-    <row r="231" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="231" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>10</v>
       </c>
@@ -10904,11 +10942,11 @@
         <v>608354873.18599999</v>
       </c>
       <c r="N231" s="4">
-        <f t="shared" si="3"/>
+        <f>M231/L231</f>
         <v>9.9647922751144495</v>
       </c>
     </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="232" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>10</v>
       </c>
@@ -10949,11 +10987,11 @@
         <v>775985443.50600004</v>
       </c>
       <c r="N232" s="4">
-        <f t="shared" si="3"/>
+        <f>M232/L232</f>
         <v>11.159420919681812</v>
       </c>
     </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="233" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>10</v>
       </c>
@@ -10994,11 +11032,11 @@
         <v>675089583.37800002</v>
       </c>
       <c r="N233" s="4">
-        <f t="shared" si="3"/>
+        <f>M233/L233</f>
         <v>10.829103686522142</v>
       </c>
     </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="234" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>10</v>
       </c>
@@ -11039,11 +11077,11 @@
         <v>626352669.74600005</v>
       </c>
       <c r="N234" s="4">
-        <f t="shared" si="3"/>
+        <f>M234/L234</f>
         <v>10.220318179185181</v>
       </c>
     </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="235" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>10</v>
       </c>
@@ -11084,11 +11122,11 @@
         <v>722113019.53900003</v>
       </c>
       <c r="N235" s="4">
-        <f t="shared" si="3"/>
+        <f>M235/L235</f>
         <v>9.2928733419385772</v>
       </c>
     </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="236" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>10</v>
       </c>
@@ -11129,11 +11167,11 @@
         <v>709118412.08399999</v>
       </c>
       <c r="N236" s="4">
-        <f t="shared" si="3"/>
+        <f>M236/L236</f>
         <v>9.0029136776049032</v>
       </c>
     </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="237" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>10</v>
       </c>
@@ -11174,11 +11212,11 @@
         <v>765495124.55700004</v>
       </c>
       <c r="N237" s="4">
-        <f t="shared" si="3"/>
+        <f>M237/L237</f>
         <v>7.5072232064467563</v>
       </c>
     </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="238" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>10</v>
       </c>
@@ -11219,11 +11257,11 @@
         <v>773550204.68700004</v>
       </c>
       <c r="N238" s="4">
-        <f t="shared" si="3"/>
+        <f>M238/L238</f>
         <v>7.2380030464541383</v>
       </c>
     </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="239" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>10</v>
       </c>
@@ -11264,11 +11302,11 @@
         <v>823887169.005</v>
       </c>
       <c r="N239" s="4">
-        <f t="shared" si="3"/>
+        <f>M239/L239</f>
         <v>7.5478340462142599</v>
       </c>
     </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="240" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>10</v>
       </c>
@@ -11309,11 +11347,11 @@
         <v>783937909.86800003</v>
       </c>
       <c r="N240" s="4">
-        <f t="shared" si="3"/>
+        <f>M240/L240</f>
         <v>7.5506956910401275</v>
       </c>
     </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="241" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>10</v>
       </c>
@@ -11354,11 +11392,11 @@
         <v>706019084.61199999</v>
       </c>
       <c r="N241" s="4">
-        <f t="shared" si="3"/>
+        <f>M241/L241</f>
         <v>8.4715420410568072</v>
       </c>
     </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="242" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>10</v>
       </c>
@@ -11399,11 +11437,11 @@
         <v>653515167.05700004</v>
       </c>
       <c r="N242" s="4">
-        <f t="shared" si="3"/>
+        <f>M242/L242</f>
         <v>10.23642149928501</v>
       </c>
     </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="243" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>10</v>
       </c>
@@ -11444,11 +11482,11 @@
         <v>569730584.255</v>
       </c>
       <c r="N243" s="4">
-        <f t="shared" si="3"/>
+        <f>M243/L243</f>
         <v>10.3150924886603</v>
       </c>
     </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="244" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>10</v>
       </c>
@@ -11489,11 +11527,11 @@
         <v>579442191.29999995</v>
       </c>
       <c r="N244" s="4">
-        <f t="shared" si="3"/>
+        <f>M244/L244</f>
         <v>10.200919024613865</v>
       </c>
     </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="245" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>10</v>
       </c>
@@ -11534,11 +11572,11 @@
         <v>575079599.02400005</v>
       </c>
       <c r="N245" s="4">
-        <f t="shared" si="3"/>
+        <f>M245/L245</f>
         <v>10.952507511837403</v>
       </c>
     </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="246" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>10</v>
       </c>
@@ -11579,11 +11617,11 @@
         <v>609525795.39499998</v>
       </c>
       <c r="N246" s="4">
-        <f t="shared" si="3"/>
+        <f>M246/L246</f>
         <v>10.882735222062946</v>
       </c>
     </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="247" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>10</v>
       </c>
@@ -11624,11 +11662,11 @@
         <v>565980761.13399994</v>
       </c>
       <c r="N247" s="4">
-        <f t="shared" si="3"/>
+        <f>M247/L247</f>
         <v>8.0738253623280816</v>
       </c>
     </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="248" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>10</v>
       </c>
@@ -11669,11 +11707,11 @@
         <v>648477406.00899994</v>
       </c>
       <c r="N248" s="4">
-        <f t="shared" si="3"/>
+        <f>M248/L248</f>
         <v>7.4388996818586639</v>
       </c>
     </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="249" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>10</v>
       </c>
@@ -11714,11 +11752,11 @@
         <v>748707564.34000003</v>
       </c>
       <c r="N249" s="4">
-        <f t="shared" si="3"/>
+        <f>M249/L249</f>
         <v>7.2932618056692773</v>
       </c>
     </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="250" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>10</v>
       </c>
@@ -11759,11 +11797,11 @@
         <v>804304955.89499998</v>
       </c>
       <c r="N250" s="4">
-        <f t="shared" si="3"/>
+        <f>M250/L250</f>
         <v>6.9419542007587838</v>
       </c>
     </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="251" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>10</v>
       </c>
@@ -11804,11 +11842,11 @@
         <v>791978270.46599996</v>
       </c>
       <c r="N251" s="4">
-        <f t="shared" si="3"/>
+        <f>M251/L251</f>
         <v>6.8887094065985535</v>
       </c>
     </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="252" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>10</v>
       </c>
@@ -11849,11 +11887,11 @@
         <v>772659031.773</v>
       </c>
       <c r="N252" s="4">
-        <f t="shared" si="3"/>
+        <f>M252/L252</f>
         <v>7.5243919967250461</v>
       </c>
     </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="253" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>10</v>
       </c>
@@ -11894,11 +11932,11 @@
         <v>730022653.62</v>
       </c>
       <c r="N253" s="4">
-        <f t="shared" si="3"/>
+        <f>M253/L253</f>
         <v>8.3729877997195761</v>
       </c>
     </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="254" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>10</v>
       </c>
@@ -11939,11 +11977,11 @@
         <v>656162665.52199996</v>
       </c>
       <c r="N254" s="4">
-        <f t="shared" si="3"/>
+        <f>M254/L254</f>
         <v>9.3926900404408222</v>
       </c>
     </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="255" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>10</v>
       </c>
@@ -11984,11 +12022,11 @@
         <v>529371053.87599999</v>
       </c>
       <c r="N255" s="4">
-        <f t="shared" si="3"/>
+        <f>M255/L255</f>
         <v>8.2873690392355428</v>
       </c>
     </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="256" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>10</v>
       </c>
@@ -12029,11 +12067,11 @@
         <v>616318296.97000003</v>
       </c>
       <c r="N256" s="4">
-        <f t="shared" si="3"/>
+        <f>M256/L256</f>
         <v>8.1366753067592636</v>
       </c>
     </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="257" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>10</v>
       </c>
@@ -12074,11 +12112,11 @@
         <v>612343289.66299999</v>
       </c>
       <c r="N257" s="4">
-        <f t="shared" si="3"/>
+        <f>M257/L257</f>
         <v>7.8649589621890863</v>
       </c>
     </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="258" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>10</v>
       </c>
@@ -12119,11 +12157,11 @@
         <v>610482360.86300004</v>
       </c>
       <c r="N258" s="4">
-        <f t="shared" si="3"/>
+        <f>M258/L258</f>
         <v>7.2379525051514548</v>
       </c>
     </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="259" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>10</v>
       </c>
@@ -12164,11 +12202,11 @@
         <v>627034059.52100003</v>
       </c>
       <c r="N259" s="4">
-        <f t="shared" ref="N259:N265" si="4">M259/L259</f>
+        <f>M259/L259</f>
         <v>7.4317763780366555</v>
       </c>
     </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="260" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>10</v>
       </c>
@@ -12209,11 +12247,11 @@
         <v>721114872.28900003</v>
       </c>
       <c r="N260" s="4">
-        <f t="shared" si="4"/>
+        <f>M260/L260</f>
         <v>6.5468829294397217</v>
       </c>
     </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="261" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>10</v>
       </c>
@@ -12254,11 +12292,11 @@
         <v>736890195.398</v>
       </c>
       <c r="N261" s="4">
-        <f t="shared" si="4"/>
+        <f>M261/L261</f>
         <v>6.272339455918341</v>
       </c>
     </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="262" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>10</v>
       </c>
@@ -12299,11 +12337,11 @@
         <v>805294154.94200003</v>
       </c>
       <c r="N262" s="4">
-        <f t="shared" si="4"/>
+        <f>M262/L262</f>
         <v>7.6078707630758267</v>
       </c>
     </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="263" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>10</v>
       </c>
@@ -12344,11 +12382,11 @@
         <v>889943834.66700006</v>
       </c>
       <c r="N263" s="4">
-        <f t="shared" si="4"/>
+        <f>M263/L263</f>
         <v>7.6642739245462321</v>
       </c>
     </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="264" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>10</v>
       </c>
@@ -12389,11 +12427,11 @@
         <v>787229098.75199997</v>
       </c>
       <c r="N264" s="4">
-        <f t="shared" si="4"/>
+        <f>M264/L264</f>
         <v>7.9901003834152347</v>
       </c>
     </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="265" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>10</v>
       </c>
@@ -12434,22 +12472,22 @@
         <v>863950829.01600003</v>
       </c>
       <c r="N265" s="4">
-        <f t="shared" si="4"/>
+        <f>M265/L265</f>
         <v>9.2527770810061511</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:B13 D1:D13 E1:E13 F1:F13 G1:H13 I1:I3 I5:I13 I4 J4 J1:J3 J5:J13 M4 M2:M3 M5:M13 L4 L1:L3 L5:L13" numberStoredAsText="1"/>
-  </ignoredErrors>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
